--- a/dist/VSM_station_import_template.xlsx
+++ b/dist/VSM_station_import_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="站別資料" sheetId="1" r:id="R156bb12adeef490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="站別資料" sheetId="1" r:id="R1a82c1df9c0e487d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +57,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -67,6 +67,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF0A4C91"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF5BF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCEAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -220,7 +230,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="89">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -352,6 +362,82 @@
     <x:xf numFmtId="201" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -564,7 +650,7 @@
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="9" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
@@ -591,7 +677,7 @@
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>Edit the yellow cells. 前 4 列為範例，可覆寫或刪除內容；最多匯入 10 個站別。</x:v>
+        <x:v>Edit the yellow cells. 前 4 列為範例，可覆寫或刪除內容；最多匯入 20 個站別。</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3"/>
@@ -644,7 +730,7 @@
         <x:v>OCTb (min)</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
-        <x:v>OCTc (min)</x:v>
+        <x:v>C/O Changeover Time (min) / 換線／切換時間</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
         <x:v>Operators / 人數</x:v>
@@ -928,107 +1014,269 @@
       <x:c r="L15" s="57"/>
       <x:c r="M15" s="58"/>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="1"/>
-      <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1"/>
-      <x:c r="D16" s="1"/>
-      <x:c r="E16" s="1"/>
-      <x:c r="F16" s="1"/>
-      <x:c r="G16" s="1"/>
-      <x:c r="H16" s="1"/>
-      <x:c r="I16" s="1"/>
-      <x:c r="J16" s="1"/>
-      <x:c r="K16" s="1"/>
-      <x:c r="L16" s="1"/>
-      <x:c r="M16" s="1"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="31" t="str">
+    <x:row r="16" ht="20" customHeight="1">
+      <x:c r="A16" s="70" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="72"/>
+      <x:c r="C16" s="72"/>
+      <x:c r="D16" s="76"/>
+      <x:c r="E16" s="76"/>
+      <x:c r="F16" s="76"/>
+      <x:c r="G16" s="76"/>
+      <x:c r="H16" s="76"/>
+      <x:c r="I16" s="78"/>
+      <x:c r="J16" s="78"/>
+      <x:c r="K16" s="78"/>
+      <x:c r="L16" s="78"/>
+      <x:c r="M16" s="82"/>
+    </x:row>
+    <x:row r="17" ht="20" customHeight="1">
+      <x:c r="A17" s="70" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="72"/>
+      <x:c r="C17" s="72"/>
+      <x:c r="D17" s="76"/>
+      <x:c r="E17" s="76"/>
+      <x:c r="F17" s="76"/>
+      <x:c r="G17" s="76"/>
+      <x:c r="H17" s="76"/>
+      <x:c r="I17" s="78"/>
+      <x:c r="J17" s="78"/>
+      <x:c r="K17" s="78"/>
+      <x:c r="L17" s="78"/>
+      <x:c r="M17" s="82"/>
+    </x:row>
+    <x:row r="18" ht="20" customHeight="1">
+      <x:c r="A18" s="70" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="72"/>
+      <x:c r="C18" s="72"/>
+      <x:c r="D18" s="76"/>
+      <x:c r="E18" s="76"/>
+      <x:c r="F18" s="76"/>
+      <x:c r="G18" s="76"/>
+      <x:c r="H18" s="76"/>
+      <x:c r="I18" s="78"/>
+      <x:c r="J18" s="78"/>
+      <x:c r="K18" s="78"/>
+      <x:c r="L18" s="78"/>
+      <x:c r="M18" s="82"/>
+    </x:row>
+    <x:row r="19" ht="20" customHeight="1">
+      <x:c r="A19" s="70" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="72"/>
+      <x:c r="C19" s="72"/>
+      <x:c r="D19" s="76"/>
+      <x:c r="E19" s="76"/>
+      <x:c r="F19" s="76"/>
+      <x:c r="G19" s="76"/>
+      <x:c r="H19" s="76"/>
+      <x:c r="I19" s="78"/>
+      <x:c r="J19" s="78"/>
+      <x:c r="K19" s="78"/>
+      <x:c r="L19" s="78"/>
+      <x:c r="M19" s="82"/>
+    </x:row>
+    <x:row r="20" ht="20" customHeight="1">
+      <x:c r="A20" s="70" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="72"/>
+      <x:c r="C20" s="72"/>
+      <x:c r="D20" s="76"/>
+      <x:c r="E20" s="76"/>
+      <x:c r="F20" s="76"/>
+      <x:c r="G20" s="76"/>
+      <x:c r="H20" s="76"/>
+      <x:c r="I20" s="78"/>
+      <x:c r="J20" s="78"/>
+      <x:c r="K20" s="78"/>
+      <x:c r="L20" s="78"/>
+      <x:c r="M20" s="82"/>
+    </x:row>
+    <x:row r="21" ht="20" customHeight="1">
+      <x:c r="A21" s="70" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="72"/>
+      <x:c r="C21" s="72"/>
+      <x:c r="D21" s="76"/>
+      <x:c r="E21" s="76"/>
+      <x:c r="F21" s="76"/>
+      <x:c r="G21" s="76"/>
+      <x:c r="H21" s="76"/>
+      <x:c r="I21" s="78"/>
+      <x:c r="J21" s="78"/>
+      <x:c r="K21" s="78"/>
+      <x:c r="L21" s="78"/>
+      <x:c r="M21" s="82"/>
+    </x:row>
+    <x:row r="22" ht="20" customHeight="1">
+      <x:c r="A22" s="70" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" s="72"/>
+      <x:c r="C22" s="72"/>
+      <x:c r="D22" s="76"/>
+      <x:c r="E22" s="76"/>
+      <x:c r="F22" s="76"/>
+      <x:c r="G22" s="76"/>
+      <x:c r="H22" s="76"/>
+      <x:c r="I22" s="78"/>
+      <x:c r="J22" s="78"/>
+      <x:c r="K22" s="78"/>
+      <x:c r="L22" s="78"/>
+      <x:c r="M22" s="82"/>
+    </x:row>
+    <x:row r="23" ht="20" customHeight="1">
+      <x:c r="A23" s="70" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" s="72"/>
+      <x:c r="C23" s="72"/>
+      <x:c r="D23" s="76"/>
+      <x:c r="E23" s="76"/>
+      <x:c r="F23" s="76"/>
+      <x:c r="G23" s="76"/>
+      <x:c r="H23" s="76"/>
+      <x:c r="I23" s="78"/>
+      <x:c r="J23" s="78"/>
+      <x:c r="K23" s="78"/>
+      <x:c r="L23" s="78"/>
+      <x:c r="M23" s="82"/>
+    </x:row>
+    <x:row r="24" ht="20" customHeight="1">
+      <x:c r="A24" s="70" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" s="72"/>
+      <x:c r="C24" s="72"/>
+      <x:c r="D24" s="76"/>
+      <x:c r="E24" s="76"/>
+      <x:c r="F24" s="76"/>
+      <x:c r="G24" s="76"/>
+      <x:c r="H24" s="76"/>
+      <x:c r="I24" s="78"/>
+      <x:c r="J24" s="78"/>
+      <x:c r="K24" s="78"/>
+      <x:c r="L24" s="78"/>
+      <x:c r="M24" s="82"/>
+    </x:row>
+    <x:row r="25" ht="20" customHeight="1">
+      <x:c r="A25" s="71" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" s="73"/>
+      <x:c r="C25" s="73"/>
+      <x:c r="D25" s="77"/>
+      <x:c r="E25" s="77"/>
+      <x:c r="F25" s="77"/>
+      <x:c r="G25" s="77"/>
+      <x:c r="H25" s="77"/>
+      <x:c r="I25" s="79"/>
+      <x:c r="J25" s="79"/>
+      <x:c r="K25" s="79"/>
+      <x:c r="L25" s="79"/>
+      <x:c r="M25" s="83"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="86" t="str">
         <x:v>Input rules / 填寫規則</x:v>
       </x:c>
-      <x:c r="B17" s="32"/>
-      <x:c r="C17" s="32"/>
-      <x:c r="D17" s="32"/>
-      <x:c r="E17" s="32"/>
-      <x:c r="F17" s="32"/>
-      <x:c r="G17" s="32"/>
-      <x:c r="H17" s="32"/>
-      <x:c r="I17" s="32"/>
-      <x:c r="J17" s="32"/>
-      <x:c r="K17" s="32"/>
-      <x:c r="L17" s="32"/>
-      <x:c r="M17" s="33"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="34" t="str">
+      <x:c r="B27" s="87"/>
+      <x:c r="C27" s="87"/>
+      <x:c r="D27" s="87"/>
+      <x:c r="E27" s="87"/>
+      <x:c r="F27" s="87"/>
+      <x:c r="G27" s="87"/>
+      <x:c r="H27" s="87"/>
+      <x:c r="I27" s="87"/>
+      <x:c r="J27" s="87"/>
+      <x:c r="K27" s="87"/>
+      <x:c r="L27" s="87"/>
+      <x:c r="M27" s="88"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="34" t="str">
         <x:v>Required: Station, Process, CT. 必要欄位為站別、製程名稱與 CT，CT 必須大於 0。</x:v>
       </x:c>
-      <x:c r="B18" s="34"/>
-      <x:c r="C18" s="34"/>
-      <x:c r="D18" s="34"/>
-      <x:c r="E18" s="34"/>
-      <x:c r="F18" s="34"/>
-      <x:c r="G18" s="34"/>
-      <x:c r="H18" s="34"/>
-      <x:c r="I18" s="34"/>
-      <x:c r="J18" s="34"/>
-      <x:c r="K18" s="34"/>
-      <x:c r="L18" s="34"/>
-      <x:c r="M18" s="34"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="34" t="str">
-        <x:v>Operators and machines must be at least 1. 人數與並行機台至少為 1，WIP、緩衝與 OCT 不可為負數。</x:v>
-      </x:c>
-      <x:c r="B19" s="34"/>
-      <x:c r="C19" s="34"/>
-      <x:c r="D19" s="34"/>
-      <x:c r="E19" s="34"/>
-      <x:c r="F19" s="34"/>
-      <x:c r="G19" s="34"/>
-      <x:c r="H19" s="34"/>
-      <x:c r="I19" s="34"/>
-      <x:c r="J19" s="34"/>
-      <x:c r="K19" s="34"/>
-      <x:c r="L19" s="34"/>
-      <x:c r="M19" s="34"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="34" t="str">
+      <x:c r="B28" s="34"/>
+      <x:c r="C28" s="34"/>
+      <x:c r="D28" s="34"/>
+      <x:c r="E28" s="34"/>
+      <x:c r="F28" s="34"/>
+      <x:c r="G28" s="34"/>
+      <x:c r="H28" s="34"/>
+      <x:c r="I28" s="34"/>
+      <x:c r="J28" s="34"/>
+      <x:c r="K28" s="34"/>
+      <x:c r="L28" s="34"/>
+      <x:c r="M28" s="34"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="34" t="str">
+        <x:v>Operators and machines must be at least 1. 人數與並行機台至少為 1，WIP、緩衝、OCT 與 C/O 不可為負數。</x:v>
+      </x:c>
+      <x:c r="B29" s="34"/>
+      <x:c r="C29" s="34"/>
+      <x:c r="D29" s="34"/>
+      <x:c r="E29" s="34"/>
+      <x:c r="F29" s="34"/>
+      <x:c r="G29" s="34"/>
+      <x:c r="H29" s="34"/>
+      <x:c r="I29" s="34"/>
+      <x:c r="J29" s="34"/>
+      <x:c r="K29" s="34"/>
+      <x:c r="L29" s="34"/>
+      <x:c r="M29" s="34"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="34" t="str">
         <x:v>Yield accepts 98, 98% or 0.98. 良率輸入後都會轉換為 98%。</x:v>
       </x:c>
-      <x:c r="B20" s="34"/>
-      <x:c r="C20" s="34"/>
-      <x:c r="D20" s="34"/>
-      <x:c r="E20" s="34"/>
-      <x:c r="F20" s="34"/>
-      <x:c r="G20" s="34"/>
-      <x:c r="H20" s="34"/>
-      <x:c r="I20" s="34"/>
-      <x:c r="J20" s="34"/>
-      <x:c r="K20" s="34"/>
-      <x:c r="L20" s="34"/>
-      <x:c r="M20" s="34"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="34" t="str">
+      <x:c r="B30" s="34"/>
+      <x:c r="C30" s="34"/>
+      <x:c r="D30" s="34"/>
+      <x:c r="E30" s="34"/>
+      <x:c r="F30" s="34"/>
+      <x:c r="G30" s="34"/>
+      <x:c r="H30" s="34"/>
+      <x:c r="I30" s="34"/>
+      <x:c r="J30" s="34"/>
+      <x:c r="K30" s="34"/>
+      <x:c r="L30" s="34"/>
+      <x:c r="M30" s="34"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="34" t="str">
         <x:v>Import replaces current stations; blank rows are ignored. 匯入會取代網頁目前站別資料，空白列不會匯入。</x:v>
       </x:c>
-      <x:c r="B21" s="34"/>
-      <x:c r="C21" s="34"/>
-      <x:c r="D21" s="34"/>
-      <x:c r="E21" s="34"/>
-      <x:c r="F21" s="34"/>
-      <x:c r="G21" s="34"/>
-      <x:c r="H21" s="34"/>
-      <x:c r="I21" s="34"/>
-      <x:c r="J21" s="34"/>
-      <x:c r="K21" s="34"/>
-      <x:c r="L21" s="34"/>
-      <x:c r="M21" s="34"/>
+      <x:c r="B31" s="34"/>
+      <x:c r="C31" s="34"/>
+      <x:c r="D31" s="34"/>
+      <x:c r="E31" s="34"/>
+      <x:c r="F31" s="34"/>
+      <x:c r="G31" s="34"/>
+      <x:c r="H31" s="34"/>
+      <x:c r="I31" s="34"/>
+      <x:c r="J31" s="34"/>
+      <x:c r="K31" s="34"/>
+      <x:c r="L31" s="34"/>
+      <x:c r="M31" s="34"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A27:M27"/>
+    <x:mergeCell ref="A28:M28"/>
+    <x:mergeCell ref="A29:M29"/>
+    <x:mergeCell ref="A30:M30"/>
+    <x:mergeCell ref="A31:M31"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>